--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>-</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file NON-VA MEDS (55.05)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>NonvaMeds5505.orderNumber</t>
+    <t>NonvaMeds5505.disclaimer</t>
   </si>
   <si>
     <t>1</t>
@@ -255,12 +255,6 @@
   <si>
     <t xml:space="preserve">Element
 </t>
-  </si>
-  <si>
-    <t>ORDER NUMBER (-7)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.disclaimer</t>
   </si>
   <si>
     <t>DISCLAIMER (-10)</t>
@@ -571,11 +565,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ5"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.26953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.26953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="26.4296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="26.4296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -605,7 +599,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="29.26953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="26.4296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1021,106 +1015,6 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF5" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="105">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>NonvaMeds5505.disclaimer</t>
+    <t>NonvaMeds5505.orderNumber</t>
   </si>
   <si>
     <t>1</t>
@@ -255,6 +255,72 @@
   <si>
     <t xml:space="preserve">Element
 </t>
+  </si>
+  <si>
+    <t>ORDER NUMBER (-7)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.orderableItem</t>
+  </si>
+  <si>
+    <t>ORDERABLE ITEM (-.01)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.dispenseDrug</t>
+  </si>
+  <si>
+    <t>DISPENSE DRUG (-1)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.medicationRoute</t>
+  </si>
+  <si>
+    <t>MEDICATION ROUTE (-3)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.schedule</t>
+  </si>
+  <si>
+    <t>SCHEDULE (-4)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.status</t>
+  </si>
+  <si>
+    <t>STATUS (-5)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.documentedDate</t>
+  </si>
+  <si>
+    <t>DOCUMENTED DATE (-11)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.documentedBy</t>
+  </si>
+  <si>
+    <t>DOCUMENTED BY (-12)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.comments</t>
+  </si>
+  <si>
+    <t>COMMENTS (-14)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.indicationForUse</t>
+  </si>
+  <si>
+    <t>INDICATION FOR USE (-15)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.sig</t>
+  </si>
+  <si>
+    <t>SIG (-16)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.disclaimer</t>
   </si>
   <si>
     <t>DISCLAIMER (-10)</t>
@@ -565,11 +631,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ4"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="26.4296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.4296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.91015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.91015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -599,7 +665,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="26.4296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.91015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1015,6 +1081,1106 @@
         <v>72</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF5" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,6 +260,12 @@
     <t>ORDER NUMBER (-7)</t>
   </si>
   <si>
+    <t>NonvaMeds5505.ien</t>
+  </si>
+  <si>
+    <t>IEN (-.001)</t>
+  </si>
+  <si>
     <t>NonvaMeds5505.orderableItem</t>
   </si>
   <si>
@@ -270,6 +276,12 @@
   </si>
   <si>
     <t>DISPENSE DRUG (-1)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.dosage</t>
+  </si>
+  <si>
+    <t>DOSAGE (-2)</t>
   </si>
   <si>
     <t>NonvaMeds5505.medicationRoute</t>
@@ -631,7 +643,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.91015625" customWidth="true" bestFit="true"/>
@@ -2181,6 +2193,206 @@
         <v>72</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file NON-VA MEDS (55.05)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source NON-VA MEDS (55.05)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>NonvaMeds5505.orderNumber</t>
+    <t>NonvaMeds5505.orderableItem</t>
   </si>
   <si>
     <t>1</t>
@@ -257,6 +257,72 @@
 </t>
   </si>
   <si>
+    <t>ORDERABLE ITEM (-.01)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.dispenseDrug</t>
+  </si>
+  <si>
+    <t>DISPENSE DRUG (-1)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.dosage</t>
+  </si>
+  <si>
+    <t>DOSAGE (-2)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.medicationRoute</t>
+  </si>
+  <si>
+    <t>MEDICATION ROUTE (-3)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.schedule</t>
+  </si>
+  <si>
+    <t>SCHEDULE (-4)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.status</t>
+  </si>
+  <si>
+    <t>STATUS (-5)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.documentedDate</t>
+  </si>
+  <si>
+    <t>DOCUMENTED DATE (-11)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.documentedBy</t>
+  </si>
+  <si>
+    <t>DOCUMENTED BY (-12)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.comments</t>
+  </si>
+  <si>
+    <t>COMMENTS (-14)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.indicationForUse</t>
+  </si>
+  <si>
+    <t>INDICATION FOR USE (-15)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.sig</t>
+  </si>
+  <si>
+    <t>SIG (-16)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.orderNumber</t>
+  </si>
+  <si>
     <t>ORDER NUMBER (-7)</t>
   </si>
   <si>
@@ -264,72 +330,6 @@
   </si>
   <si>
     <t>IEN (-.001)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.orderableItem</t>
-  </si>
-  <si>
-    <t>ORDERABLE ITEM (-.01)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.dispenseDrug</t>
-  </si>
-  <si>
-    <t>DISPENSE DRUG (-1)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.dosage</t>
-  </si>
-  <si>
-    <t>DOSAGE (-2)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.medicationRoute</t>
-  </si>
-  <si>
-    <t>MEDICATION ROUTE (-3)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.schedule</t>
-  </si>
-  <si>
-    <t>SCHEDULE (-4)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.status</t>
-  </si>
-  <si>
-    <t>STATUS (-5)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.documentedDate</t>
-  </si>
-  <si>
-    <t>DOCUMENTED DATE (-11)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.documentedBy</t>
-  </si>
-  <si>
-    <t>DOCUMENTED BY (-12)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.comments</t>
-  </si>
-  <si>
-    <t>COMMENTS (-14)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.indicationForUse</t>
-  </si>
-  <si>
-    <t>INDICATION FOR USE (-15)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.sig</t>
-  </si>
-  <si>
-    <t>SIG (-16)</t>
   </si>
   <si>
     <t>NonvaMeds5505.disclaimer</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>NonvaMeds5505.orderableItem</t>
+    <t>NonvaMeds5505.orderNumber</t>
   </si>
   <si>
     <t>1</t>
@@ -257,6 +257,18 @@
 </t>
   </si>
   <si>
+    <t>ORDER NUMBER (-7)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.ien</t>
+  </si>
+  <si>
+    <t>IEN (-.001)</t>
+  </si>
+  <si>
+    <t>NonvaMeds5505.orderableItem</t>
+  </si>
+  <si>
     <t>ORDERABLE ITEM (-.01)</t>
   </si>
   <si>
@@ -318,18 +330,6 @@
   </si>
   <si>
     <t>SIG (-16)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.orderNumber</t>
-  </si>
-  <si>
-    <t>ORDER NUMBER (-7)</t>
-  </si>
-  <si>
-    <t>NonvaMeds5505.ien</t>
-  </si>
-  <si>
-    <t>IEN (-.001)</t>
   </si>
   <si>
     <t>NonvaMeds5505.disclaimer</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-NonvaMeds5505.xlsx
+++ b/docs/StructureDefinition-NonvaMeds5505.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
